--- a/site/nb_leads.xlsx
+++ b/site/nb_leads.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="New Brunswick" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="New Brunswick" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/site/nb_leads.xlsx
+++ b/site/nb_leads.xlsx
@@ -620,7 +620,7 @@
         <v>325</v>
       </c>
       <c r="U2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V2" t="n">
         <v>45.68611</v>
@@ -690,7 +690,7 @@
         <v>325</v>
       </c>
       <c r="U3" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V3" t="n">
         <v>45.3264</v>
@@ -760,7 +760,7 @@
         <v>325</v>
       </c>
       <c r="U4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V4" t="n">
         <v>45.41948</v>
@@ -830,7 +830,7 @@
         <v>325</v>
       </c>
       <c r="U5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V5" t="n">
         <v>45.42362</v>
@@ -900,7 +900,7 @@
         <v>325</v>
       </c>
       <c r="U6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V6" t="n">
         <v>45.25751</v>
@@ -970,7 +970,7 @@
         <v>325</v>
       </c>
       <c r="U7" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V7" t="n">
         <v>45.86251</v>
@@ -1040,7 +1040,7 @@
         <v>325</v>
       </c>
       <c r="U8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V8" t="n">
         <v>45.84944</v>
@@ -1110,7 +1110,7 @@
         <v>325</v>
       </c>
       <c r="U9" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V9" t="n">
         <v>45.55224</v>
@@ -1180,7 +1180,7 @@
         <v>325</v>
       </c>
       <c r="U10" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V10" t="n">
         <v>45.63113</v>
@@ -1250,7 +1250,7 @@
         <v>325</v>
       </c>
       <c r="U11" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V11" t="n">
         <v>45.57888</v>
@@ -1320,7 +1320,7 @@
         <v>325</v>
       </c>
       <c r="U12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V12" t="n">
         <v>45.58501</v>
@@ -1390,7 +1390,7 @@
         <v>325</v>
       </c>
       <c r="U13" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V13" t="n">
         <v>45.49222</v>
@@ -1460,7 +1460,7 @@
         <v>325</v>
       </c>
       <c r="U14" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V14" t="n">
         <v>47.67266</v>
@@ -1530,7 +1530,7 @@
         <v>325</v>
       </c>
       <c r="U15" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V15" t="n">
         <v>47.43555</v>
@@ -1600,7 +1600,7 @@
         <v>325</v>
       </c>
       <c r="U16" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V16" t="n">
         <v>47.79002</v>
@@ -1670,7 +1670,7 @@
         <v>325</v>
       </c>
       <c r="U17" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V17" t="n">
         <v>47.87583</v>
@@ -1740,7 +1740,7 @@
         <v>325</v>
       </c>
       <c r="U18" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V18" t="n">
         <v>45.29809</v>
@@ -1810,7 +1810,7 @@
         <v>325</v>
       </c>
       <c r="U19" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V19" t="n">
         <v>45.35473</v>
@@ -1880,7 +1880,7 @@
         <v>325</v>
       </c>
       <c r="U20" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V20" t="n">
         <v>45.0575</v>
@@ -1950,7 +1950,7 @@
         <v>325</v>
       </c>
       <c r="U21" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V21" t="n">
         <v>45.22445</v>
@@ -2020,7 +2020,7 @@
         <v>325</v>
       </c>
       <c r="U22" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V22" t="n">
         <v>45.74919</v>
@@ -2090,7 +2090,7 @@
         <v>325</v>
       </c>
       <c r="U23" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V23" t="n">
         <v>45.64444</v>
@@ -2160,7 +2160,7 @@
         <v>325</v>
       </c>
       <c r="U24" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V24" t="n">
         <v>45.65473</v>
@@ -2230,7 +2230,7 @@
         <v>325</v>
       </c>
       <c r="U25" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V25" t="n">
         <v>45.71305</v>
@@ -2300,7 +2300,7 @@
         <v>325</v>
       </c>
       <c r="U26" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V26" t="n">
         <v>45.57584</v>
@@ -2370,7 +2370,7 @@
         <v>325</v>
       </c>
       <c r="U27" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V27" t="n">
         <v>45.71612</v>
@@ -2440,7 +2440,7 @@
         <v>325</v>
       </c>
       <c r="U28" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V28" t="n">
         <v>44.68722</v>
@@ -2510,7 +2510,7 @@
         <v>325</v>
       </c>
       <c r="U29" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V29" t="n">
         <v>45.22336</v>
@@ -2580,7 +2580,7 @@
         <v>325</v>
       </c>
       <c r="U30" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V30" t="n">
         <v>45.18306</v>
@@ -2650,7 +2650,7 @@
         <v>325</v>
       </c>
       <c r="U31" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V31" t="n">
         <v>45.185</v>
@@ -2720,7 +2720,7 @@
         <v>325</v>
       </c>
       <c r="U32" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V32" t="n">
         <v>45.19833</v>
@@ -2790,7 +2790,7 @@
         <v>325</v>
       </c>
       <c r="U33" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V33" t="n">
         <v>45.77334</v>
@@ -2860,7 +2860,7 @@
         <v>325</v>
       </c>
       <c r="U34" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V34" t="n">
         <v>45.10085</v>
@@ -2930,7 +2930,7 @@
         <v>325</v>
       </c>
       <c r="U35" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V35" t="n">
         <v>45.10751</v>
@@ -3000,7 +3000,7 @@
         <v>325</v>
       </c>
       <c r="U36" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V36" t="n">
         <v>45.2222</v>
@@ -3070,7 +3070,7 @@
         <v>325</v>
       </c>
       <c r="U37" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V37" t="n">
         <v>45.76641</v>
@@ -3140,7 +3140,7 @@
         <v>325</v>
       </c>
       <c r="U38" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V38" t="n">
         <v>45.82642</v>
@@ -3210,7 +3210,7 @@
         <v>325</v>
       </c>
       <c r="U39" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V39" t="n">
         <v>45.21004</v>
@@ -3280,7 +3280,7 @@
         <v>325</v>
       </c>
       <c r="U40" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V40" t="n">
         <v>45.21809</v>
@@ -3350,7 +3350,7 @@
         <v>325</v>
       </c>
       <c r="U41" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V41" t="n">
         <v>45.4317</v>
@@ -3420,7 +3420,7 @@
         <v>325</v>
       </c>
       <c r="U42" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V42" t="n">
         <v>46.56723</v>
@@ -3490,7 +3490,7 @@
         <v>325</v>
       </c>
       <c r="U43" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V43" t="n">
         <v>47.38114</v>
@@ -3560,7 +3560,7 @@
         <v>325</v>
       </c>
       <c r="U44" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V44" t="n">
         <v>47.7214</v>
@@ -3626,7 +3626,7 @@
         <v>325</v>
       </c>
       <c r="U45" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V45" t="n">
         <v>47.53281</v>
@@ -3696,7 +3696,7 @@
         <v>325</v>
       </c>
       <c r="U46" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V46" t="n">
         <v>47.61694</v>
@@ -3766,7 +3766,7 @@
         <v>325</v>
       </c>
       <c r="U47" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V47" t="n">
         <v>47.55974</v>
@@ -3836,7 +3836,7 @@
         <v>325</v>
       </c>
       <c r="U48" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V48" t="n">
         <v>47.42863</v>
@@ -3906,7 +3906,7 @@
         <v>325</v>
       </c>
       <c r="U49" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V49" t="n">
         <v>47.47889</v>
@@ -3976,7 +3976,7 @@
         <v>325</v>
       </c>
       <c r="U50" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V50" t="n">
         <v>47.82002</v>
@@ -4046,7 +4046,7 @@
         <v>325</v>
       </c>
       <c r="U51" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V51" t="n">
         <v>45.79642</v>
@@ -4116,7 +4116,7 @@
         <v>325</v>
       </c>
       <c r="U52" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V52" t="n">
         <v>45.93834</v>
@@ -4186,7 +4186,7 @@
         <v>325</v>
       </c>
       <c r="U53" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V53" t="n">
         <v>47.42337</v>
@@ -4256,7 +4256,7 @@
         <v>325</v>
       </c>
       <c r="U54" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V54" t="n">
         <v>47.72836</v>
@@ -4326,7 +4326,7 @@
         <v>300</v>
       </c>
       <c r="U55" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V55" t="n">
         <v>47.0005</v>
@@ -4396,7 +4396,7 @@
         <v>325</v>
       </c>
       <c r="U56" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V56" t="n">
         <v>47.50967</v>
@@ -4466,7 +4466,7 @@
         <v>325</v>
       </c>
       <c r="U57" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V57" t="n">
         <v>47.24128</v>
@@ -4536,7 +4536,7 @@
         <v>325</v>
       </c>
       <c r="U58" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V58" t="n">
         <v>47.05753</v>
@@ -4602,7 +4602,7 @@
         <v>325</v>
       </c>
       <c r="U59" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V59" t="n">
         <v>47.04892</v>
@@ -4672,7 +4672,7 @@
         <v>325</v>
       </c>
       <c r="U60" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V60" t="n">
         <v>47.39779</v>
@@ -4742,7 +4742,7 @@
         <v>325</v>
       </c>
       <c r="U61" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V61" t="n">
         <v>47.69693</v>
@@ -4812,7 +4812,7 @@
         <v>325</v>
       </c>
       <c r="U62" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V62" t="n">
         <v>47.82638</v>
@@ -4882,7 +4882,7 @@
         <v>325</v>
       </c>
       <c r="U63" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V63" t="n">
         <v>47.77225</v>
@@ -4952,7 +4952,7 @@
         <v>325</v>
       </c>
       <c r="U64" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V64" t="n">
         <v>47.84393</v>
@@ -5022,7 +5022,7 @@
         <v>325</v>
       </c>
       <c r="U65" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V65" t="n">
         <v>47.85405</v>
@@ -5092,7 +5092,7 @@
         <v>325</v>
       </c>
       <c r="U66" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V66" t="n">
         <v>47.85948</v>
@@ -5162,7 +5162,7 @@
         <v>325</v>
       </c>
       <c r="U67" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V67" t="n">
         <v>47.6717</v>
@@ -5232,7 +5232,7 @@
         <v>325</v>
       </c>
       <c r="U68" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V68" t="n">
         <v>47.38142</v>
@@ -5302,7 +5302,7 @@
         <v>325</v>
       </c>
       <c r="U69" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V69" t="n">
         <v>47.67261</v>
@@ -5372,7 +5372,7 @@
         <v>325</v>
       </c>
       <c r="U70" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V70" t="n">
         <v>47.67059</v>
@@ -5438,7 +5438,7 @@
         <v>325</v>
       </c>
       <c r="U71" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V71" t="n">
         <v>47.66892</v>
@@ -5508,7 +5508,7 @@
         <v>300</v>
       </c>
       <c r="U72" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V72" t="n">
         <v>47.78952</v>
@@ -5578,7 +5578,7 @@
         <v>325</v>
       </c>
       <c r="U73" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V73" t="n">
         <v>47.76978</v>
@@ -5648,7 +5648,7 @@
         <v>325</v>
       </c>
       <c r="U74" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V74" t="n">
         <v>45.93698</v>
@@ -5718,7 +5718,7 @@
         <v>325</v>
       </c>
       <c r="U75" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V75" t="n">
         <v>47.80197</v>
@@ -5788,7 +5788,7 @@
         <v>325</v>
       </c>
       <c r="U76" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V76" t="n">
         <v>47.77223</v>
@@ -5858,7 +5858,7 @@
         <v>325</v>
       </c>
       <c r="U77" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V77" t="n">
         <v>47.85614</v>
@@ -5928,7 +5928,7 @@
         <v>325</v>
       </c>
       <c r="U78" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V78" t="n">
         <v>47.85142</v>
@@ -5998,7 +5998,7 @@
         <v>325</v>
       </c>
       <c r="U79" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V79" t="n">
         <v>47.83336</v>
@@ -6068,7 +6068,7 @@
         <v>325</v>
       </c>
       <c r="U80" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V80" t="n">
         <v>47.40642</v>
@@ -6138,7 +6138,7 @@
         <v>325</v>
       </c>
       <c r="U81" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V81" t="n">
         <v>47.47173</v>
@@ -6208,7 +6208,7 @@
         <v>325</v>
       </c>
       <c r="U82" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V82" t="n">
         <v>47.4842</v>
@@ -6278,7 +6278,7 @@
         <v>325</v>
       </c>
       <c r="U83" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V83" t="n">
         <v>47.2053</v>
@@ -6348,7 +6348,7 @@
         <v>325</v>
       </c>
       <c r="U84" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V84" t="n">
         <v>47.07114</v>
@@ -6378,7 +6378,7 @@
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Rare earths</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -6418,7 +6418,7 @@
         <v>325</v>
       </c>
       <c r="U85" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V85" t="n">
         <v>47.90742</v>
@@ -6488,7 +6488,7 @@
         <v>325</v>
       </c>
       <c r="U86" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V86" t="n">
         <v>47.77363</v>
@@ -6558,7 +6558,7 @@
         <v>325</v>
       </c>
       <c r="U87" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V87" t="n">
         <v>47.7842</v>
@@ -6628,7 +6628,7 @@
         <v>325</v>
       </c>
       <c r="U88" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V88" t="n">
         <v>47.79642</v>
@@ -6698,7 +6698,7 @@
         <v>325</v>
       </c>
       <c r="U89" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V89" t="n">
         <v>47.81059</v>
@@ -6768,7 +6768,7 @@
         <v>325</v>
       </c>
       <c r="U90" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V90" t="n">
         <v>47.81586</v>
@@ -6838,7 +6838,7 @@
         <v>325</v>
       </c>
       <c r="U91" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V91" t="n">
         <v>47.79531</v>
@@ -6908,7 +6908,7 @@
         <v>325</v>
       </c>
       <c r="U92" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V92" t="n">
         <v>47.80309</v>
@@ -6978,7 +6978,7 @@
         <v>325</v>
       </c>
       <c r="U93" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V93" t="n">
         <v>47.81333</v>
@@ -7048,7 +7048,7 @@
         <v>325</v>
       </c>
       <c r="U94" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V94" t="n">
         <v>47.82698</v>
@@ -7118,7 +7118,7 @@
         <v>325</v>
       </c>
       <c r="U95" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V95" t="n">
         <v>47.79809</v>
@@ -7184,7 +7184,7 @@
         <v>325</v>
       </c>
       <c r="U96" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V96" t="n">
         <v>47.8078</v>
@@ -7250,7 +7250,7 @@
         <v>325</v>
       </c>
       <c r="U97" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V97" t="n">
         <v>47.84558</v>
@@ -7320,7 +7320,7 @@
         <v>325</v>
       </c>
       <c r="U98" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V98" t="n">
         <v>47.7859</v>
@@ -7390,7 +7390,7 @@
         <v>325</v>
       </c>
       <c r="U99" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V99" t="n">
         <v>47.78583</v>
@@ -7460,7 +7460,7 @@
         <v>325</v>
       </c>
       <c r="U100" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V100" t="n">
         <v>47.44642</v>
@@ -7530,7 +7530,7 @@
         <v>325</v>
       </c>
       <c r="U101" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V101" t="n">
         <v>47.44614</v>
@@ -7600,7 +7600,7 @@
         <v>325</v>
       </c>
       <c r="U102" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V102" t="n">
         <v>47.44528</v>
@@ -7670,7 +7670,7 @@
         <v>325</v>
       </c>
       <c r="U103" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V103" t="n">
         <v>47.6975</v>
@@ -7740,7 +7740,7 @@
         <v>325</v>
       </c>
       <c r="U104" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V104" t="n">
         <v>47.74002</v>
@@ -7810,7 +7810,7 @@
         <v>325</v>
       </c>
       <c r="U105" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V105" t="n">
         <v>47.74443</v>
@@ -7880,7 +7880,7 @@
         <v>325</v>
       </c>
       <c r="U106" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V106" t="n">
         <v>47.73307</v>
@@ -7950,7 +7950,7 @@
         <v>250</v>
       </c>
       <c r="U107" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V107" t="n">
         <v>47.99669</v>
@@ -8016,7 +8016,7 @@
         <v>325</v>
       </c>
       <c r="U108" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V108" t="n">
         <v>47.34809</v>
@@ -8086,7 +8086,7 @@
         <v>325</v>
       </c>
       <c r="U109" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V109" t="n">
         <v>47.87274</v>
@@ -8156,7 +8156,7 @@
         <v>325</v>
       </c>
       <c r="U110" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V110" t="n">
         <v>47.85367</v>
@@ -8226,7 +8226,7 @@
         <v>325</v>
       </c>
       <c r="U111" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V111" t="n">
         <v>47.43975</v>
@@ -8292,7 +8292,7 @@
         <v>325</v>
       </c>
       <c r="U112" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V112" t="n">
         <v>47.53479</v>
@@ -8362,7 +8362,7 @@
         <v>275</v>
       </c>
       <c r="U113" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V113" t="n">
         <v>47.51827</v>
@@ -8432,7 +8432,7 @@
         <v>325</v>
       </c>
       <c r="U114" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V114" t="n">
         <v>47.65447</v>
@@ -8502,7 +8502,7 @@
         <v>325</v>
       </c>
       <c r="U115" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V115" t="n">
         <v>47.50586</v>
@@ -8568,7 +8568,7 @@
         <v>325</v>
       </c>
       <c r="U116" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V116" t="n">
         <v>47.76039</v>
@@ -8638,7 +8638,7 @@
         <v>325</v>
       </c>
       <c r="U117" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V117" t="n">
         <v>47.49891</v>
@@ -8704,7 +8704,7 @@
         <v>325</v>
       </c>
       <c r="U118" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V118" t="n">
         <v>47.56976</v>
@@ -8770,7 +8770,7 @@
         <v>325</v>
       </c>
       <c r="U119" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V119" t="n">
         <v>47.58865</v>
@@ -8840,7 +8840,7 @@
         <v>325</v>
       </c>
       <c r="U120" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V120" t="n">
         <v>47.60503</v>
@@ -8910,7 +8910,7 @@
         <v>325</v>
       </c>
       <c r="U121" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V121" t="n">
         <v>47.37057</v>
@@ -8980,7 +8980,7 @@
         <v>325</v>
       </c>
       <c r="U122" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V122" t="n">
         <v>47.40836</v>
@@ -9050,7 +9050,7 @@
         <v>325</v>
       </c>
       <c r="U123" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V123" t="n">
         <v>47.41142</v>
@@ -9120,7 +9120,7 @@
         <v>325</v>
       </c>
       <c r="U124" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V124" t="n">
         <v>47.38308</v>
@@ -9190,7 +9190,7 @@
         <v>325</v>
       </c>
       <c r="U125" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V125" t="n">
         <v>47.39225</v>
@@ -9260,7 +9260,7 @@
         <v>325</v>
       </c>
       <c r="U126" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V126" t="n">
         <v>47.3978</v>
@@ -9330,7 +9330,7 @@
         <v>225</v>
       </c>
       <c r="U127" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V127" t="n">
         <v>47.38474</v>
@@ -9396,7 +9396,7 @@
         <v>300</v>
       </c>
       <c r="U128" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V128" t="n">
         <v>47.40057</v>
@@ -9466,7 +9466,7 @@
         <v>325</v>
       </c>
       <c r="U129" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V129" t="n">
         <v>46.12661</v>
@@ -9536,7 +9536,7 @@
         <v>325</v>
       </c>
       <c r="U130" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V130" t="n">
         <v>46.10003</v>
@@ -9606,7 +9606,7 @@
         <v>325</v>
       </c>
       <c r="U131" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V131" t="n">
         <v>46.04169</v>
@@ -9676,7 +9676,7 @@
         <v>250</v>
       </c>
       <c r="U132" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V132" t="n">
         <v>46.00614</v>
@@ -9746,7 +9746,7 @@
         <v>325</v>
       </c>
       <c r="U133" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V133" t="n">
         <v>46.07364</v>
@@ -9812,7 +9812,7 @@
         <v>325</v>
       </c>
       <c r="U134" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V134" t="n">
         <v>47.08336</v>
@@ -9882,7 +9882,7 @@
         <v>325</v>
       </c>
       <c r="U135" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V135" t="n">
         <v>47.44919</v>
@@ -9952,7 +9952,7 @@
         <v>325</v>
       </c>
       <c r="U136" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V136" t="n">
         <v>47.32746</v>
@@ -10022,7 +10022,7 @@
         <v>325</v>
       </c>
       <c r="U137" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V137" t="n">
         <v>47.28363</v>
@@ -10092,7 +10092,7 @@
         <v>325</v>
       </c>
       <c r="U138" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V138" t="n">
         <v>46.16448</v>
@@ -10162,7 +10162,7 @@
         <v>325</v>
       </c>
       <c r="U139" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V139" t="n">
         <v>46.59921</v>
@@ -10232,7 +10232,7 @@
         <v>325</v>
       </c>
       <c r="U140" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V140" t="n">
         <v>46.60725</v>
@@ -10302,7 +10302,7 @@
         <v>325</v>
       </c>
       <c r="U141" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V141" t="n">
         <v>46.65142</v>
@@ -10372,7 +10372,7 @@
         <v>325</v>
       </c>
       <c r="U142" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V142" t="n">
         <v>47.34697</v>
@@ -10438,7 +10438,7 @@
         <v>325</v>
       </c>
       <c r="U143" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V143" t="n">
         <v>47.44808</v>
@@ -10508,7 +10508,7 @@
         <v>325</v>
       </c>
       <c r="U144" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V144" t="n">
         <v>47.31197</v>
@@ -10578,7 +10578,7 @@
         <v>325</v>
       </c>
       <c r="U145" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V145" t="n">
         <v>47.32336</v>
@@ -10648,7 +10648,7 @@
         <v>325</v>
       </c>
       <c r="U146" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V146" t="n">
         <v>47.28751</v>
@@ -10718,7 +10718,7 @@
         <v>325</v>
       </c>
       <c r="U147" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V147" t="n">
         <v>47.29558</v>
@@ -10788,7 +10788,7 @@
         <v>325</v>
       </c>
       <c r="U148" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V148" t="n">
         <v>46.54225</v>
@@ -10858,7 +10858,7 @@
         <v>325</v>
       </c>
       <c r="U149" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V149" t="n">
         <v>46.56864</v>
@@ -10928,7 +10928,7 @@
         <v>325</v>
       </c>
       <c r="U150" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V150" t="n">
         <v>46.5617</v>
@@ -10998,7 +10998,7 @@
         <v>325</v>
       </c>
       <c r="U151" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V151" t="n">
         <v>46.54003</v>
@@ -11064,7 +11064,7 @@
         <v>325</v>
       </c>
       <c r="U152" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V152" t="n">
         <v>46.53836</v>
@@ -11130,7 +11130,7 @@
         <v>325</v>
       </c>
       <c r="U153" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V153" t="n">
         <v>46.55808</v>
@@ -11200,7 +11200,7 @@
         <v>325</v>
       </c>
       <c r="U154" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V154" t="n">
         <v>46.59503</v>
@@ -11270,7 +11270,7 @@
         <v>325</v>
       </c>
       <c r="U155" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V155" t="n">
         <v>46.62447</v>
@@ -11340,7 +11340,7 @@
         <v>325</v>
       </c>
       <c r="U156" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V156" t="n">
         <v>46.61447</v>
@@ -11410,7 +11410,7 @@
         <v>325</v>
       </c>
       <c r="U157" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V157" t="n">
         <v>46.60698</v>
@@ -11476,7 +11476,7 @@
         <v>325</v>
       </c>
       <c r="U158" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V158" t="n">
         <v>47.45405</v>
@@ -11546,7 +11546,7 @@
         <v>325</v>
       </c>
       <c r="U159" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V159" t="n">
         <v>47.49919</v>
@@ -11616,7 +11616,7 @@
         <v>325</v>
       </c>
       <c r="U160" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V160" t="n">
         <v>47.30058</v>
@@ -11686,7 +11686,7 @@
         <v>325</v>
       </c>
       <c r="U161" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V161" t="n">
         <v>47.35586</v>
@@ -11756,7 +11756,7 @@
         <v>325</v>
       </c>
       <c r="U162" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V162" t="n">
         <v>47.34391</v>
@@ -11826,7 +11826,7 @@
         <v>325</v>
       </c>
       <c r="U163" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V163" t="n">
         <v>47.39641</v>
@@ -11896,7 +11896,7 @@
         <v>325</v>
       </c>
       <c r="U164" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V164" t="n">
         <v>46.59031</v>
@@ -11966,7 +11966,7 @@
         <v>325</v>
       </c>
       <c r="U165" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V165" t="n">
         <v>46.39003</v>
@@ -12036,7 +12036,7 @@
         <v>325</v>
       </c>
       <c r="U166" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V166" t="n">
         <v>46.35531</v>
@@ -12106,7 +12106,7 @@
         <v>325</v>
       </c>
       <c r="U167" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V167" t="n">
         <v>46.30614</v>
@@ -12176,7 +12176,7 @@
         <v>325</v>
       </c>
       <c r="U168" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V168" t="n">
         <v>46.47864</v>
@@ -12246,7 +12246,7 @@
         <v>325</v>
       </c>
       <c r="U169" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V169" t="n">
         <v>46.35335</v>
@@ -12316,7 +12316,7 @@
         <v>325</v>
       </c>
       <c r="U170" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V170" t="n">
         <v>46.73144</v>
@@ -12386,7 +12386,7 @@
         <v>325</v>
       </c>
       <c r="U171" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V171" t="n">
         <v>46.55059</v>
@@ -12456,7 +12456,7 @@
         <v>325</v>
       </c>
       <c r="U172" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V172" t="n">
         <v>46.36671</v>
@@ -12522,7 +12522,7 @@
         <v>325</v>
       </c>
       <c r="U173" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V173" t="n">
         <v>47.74781</v>
@@ -12588,7 +12588,7 @@
         <v>325</v>
       </c>
       <c r="U174" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V174" t="n">
         <v>47.75196</v>
@@ -12658,7 +12658,7 @@
         <v>325</v>
       </c>
       <c r="U175" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V175" t="n">
         <v>47.57281</v>
@@ -12728,7 +12728,7 @@
         <v>325</v>
       </c>
       <c r="U176" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V176" t="n">
         <v>47.55641</v>
@@ -12794,7 +12794,7 @@
         <v>325</v>
       </c>
       <c r="U177" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V177" t="n">
         <v>47.63558</v>
@@ -12864,7 +12864,7 @@
         <v>325</v>
       </c>
       <c r="U178" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V178" t="n">
         <v>47.62503</v>
@@ -12930,7 +12930,7 @@
         <v>325</v>
       </c>
       <c r="U179" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V179" t="n">
         <v>47.65831</v>
@@ -12996,7 +12996,7 @@
         <v>325</v>
       </c>
       <c r="U180" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V180" t="n">
         <v>47.37558</v>
@@ -13066,7 +13066,7 @@
         <v>325</v>
       </c>
       <c r="U181" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V181" t="n">
         <v>47.40848</v>
@@ -13132,7 +13132,7 @@
         <v>325</v>
       </c>
       <c r="U182" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V182" t="n">
         <v>47.35725</v>
@@ -13202,7 +13202,7 @@
         <v>325</v>
       </c>
       <c r="U183" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V183" t="n">
         <v>47.44981</v>
@@ -13272,7 +13272,7 @@
         <v>325</v>
       </c>
       <c r="U184" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V184" t="n">
         <v>46.37503</v>
@@ -13342,7 +13342,7 @@
         <v>325</v>
       </c>
       <c r="U185" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V185" t="n">
         <v>46.36808</v>
@@ -13412,7 +13412,7 @@
         <v>325</v>
       </c>
       <c r="U186" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V186" t="n">
         <v>46.3717</v>
@@ -13482,7 +13482,7 @@
         <v>325</v>
       </c>
       <c r="U187" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V187" t="n">
         <v>46.27392</v>
@@ -13552,7 +13552,7 @@
         <v>325</v>
       </c>
       <c r="U188" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V188" t="n">
         <v>46.3717</v>
@@ -13618,7 +13618,7 @@
         <v>325</v>
       </c>
       <c r="U189" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V189" t="n">
         <v>47.77308</v>
@@ -13684,7 +13684,7 @@
         <v>325</v>
       </c>
       <c r="U190" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V190" t="n">
         <v>47.80229</v>
@@ -13754,7 +13754,7 @@
         <v>325</v>
       </c>
       <c r="U191" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V191" t="n">
         <v>46.33197</v>
@@ -13824,7 +13824,7 @@
         <v>325</v>
       </c>
       <c r="U192" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V192" t="n">
         <v>46.48059</v>
@@ -13894,7 +13894,7 @@
         <v>325</v>
       </c>
       <c r="U193" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V193" t="n">
         <v>46.48448</v>
@@ -13964,7 +13964,7 @@
         <v>325</v>
       </c>
       <c r="U194" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V194" t="n">
         <v>46.45003</v>
@@ -14034,7 +14034,7 @@
         <v>325</v>
       </c>
       <c r="U195" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V195" t="n">
         <v>45.37697</v>
@@ -14104,7 +14104,7 @@
         <v>325</v>
       </c>
       <c r="U196" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V196" t="n">
         <v>46.0592</v>
@@ -14174,7 +14174,7 @@
         <v>325</v>
       </c>
       <c r="U197" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V197" t="n">
         <v>46.08114</v>
@@ -14244,7 +14244,7 @@
         <v>325</v>
       </c>
       <c r="U198" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V198" t="n">
         <v>46.15114</v>
@@ -14314,7 +14314,7 @@
         <v>325</v>
       </c>
       <c r="U199" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V199" t="n">
         <v>46.01169</v>
@@ -14384,7 +14384,7 @@
         <v>325</v>
       </c>
       <c r="U200" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V200" t="n">
         <v>46.13864</v>
@@ -14454,7 +14454,7 @@
         <v>325</v>
       </c>
       <c r="U201" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V201" t="n">
         <v>46.01807</v>
@@ -14524,7 +14524,7 @@
         <v>325</v>
       </c>
       <c r="U202" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V202" t="n">
         <v>46.17168</v>
@@ -14594,7 +14594,7 @@
         <v>325</v>
       </c>
       <c r="U203" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V203" t="n">
         <v>46.09837</v>
@@ -14664,7 +14664,7 @@
         <v>325</v>
       </c>
       <c r="U204" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V204" t="n">
         <v>46.09003</v>
@@ -14734,7 +14734,7 @@
         <v>325</v>
       </c>
       <c r="U205" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V205" t="n">
         <v>46.13668</v>
@@ -14804,7 +14804,7 @@
         <v>325</v>
       </c>
       <c r="U206" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V206" t="n">
         <v>46.10613</v>
@@ -14874,7 +14874,7 @@
         <v>325</v>
       </c>
       <c r="U207" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V207" t="n">
         <v>46.12975</v>
@@ -14944,7 +14944,7 @@
         <v>325</v>
       </c>
       <c r="U208" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V208" t="n">
         <v>46.09503</v>
@@ -15014,7 +15014,7 @@
         <v>300</v>
       </c>
       <c r="U209" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V209" t="n">
         <v>46.01142</v>
@@ -15084,7 +15084,7 @@
         <v>325</v>
       </c>
       <c r="U210" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V210" t="n">
         <v>46.16059</v>
@@ -15154,7 +15154,7 @@
         <v>325</v>
       </c>
       <c r="U211" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V211" t="n">
         <v>46.14197</v>
@@ -15224,7 +15224,7 @@
         <v>325</v>
       </c>
       <c r="U212" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V212" t="n">
         <v>46.01892</v>
@@ -15294,7 +15294,7 @@
         <v>325</v>
       </c>
       <c r="U213" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V213" t="n">
         <v>46.03336</v>
@@ -15364,7 +15364,7 @@
         <v>325</v>
       </c>
       <c r="U214" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V214" t="n">
         <v>46.12892</v>
@@ -15434,7 +15434,7 @@
         <v>325</v>
       </c>
       <c r="U215" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V215" t="n">
         <v>46.05446</v>
@@ -15504,7 +15504,7 @@
         <v>325</v>
       </c>
       <c r="U216" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V216" t="n">
         <v>46.11614</v>
@@ -15574,7 +15574,7 @@
         <v>325</v>
       </c>
       <c r="U217" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V217" t="n">
         <v>46.11087</v>
@@ -15644,7 +15644,7 @@
         <v>325</v>
       </c>
       <c r="U218" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V218" t="n">
         <v>46.57115</v>
@@ -15710,7 +15710,7 @@
         <v>325</v>
       </c>
       <c r="U219" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V219" t="n">
         <v>46.57836</v>
@@ -15776,7 +15776,7 @@
         <v>325</v>
       </c>
       <c r="U220" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V220" t="n">
         <v>46.53392</v>
@@ -15842,7 +15842,7 @@
         <v>325</v>
       </c>
       <c r="U221" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V221" t="n">
         <v>46.54392</v>
@@ -15908,7 +15908,7 @@
         <v>325</v>
       </c>
       <c r="U222" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V222" t="n">
         <v>46.73226</v>
@@ -15978,7 +15978,7 @@
         <v>325</v>
       </c>
       <c r="U223" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V223" t="n">
         <v>46.44281</v>
@@ -16048,7 +16048,7 @@
         <v>325</v>
       </c>
       <c r="U224" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V224" t="n">
         <v>46.39587</v>
@@ -16118,7 +16118,7 @@
         <v>325</v>
       </c>
       <c r="U225" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V225" t="n">
         <v>46.12281</v>
@@ -16188,7 +16188,7 @@
         <v>325</v>
       </c>
       <c r="U226" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V226" t="n">
         <v>46.14726</v>
@@ -16258,7 +16258,7 @@
         <v>325</v>
       </c>
       <c r="U227" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V227" t="n">
         <v>46.04281</v>
@@ -16328,7 +16328,7 @@
         <v>325</v>
       </c>
       <c r="U228" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V228" t="n">
         <v>46.04085</v>
@@ -16398,7 +16398,7 @@
         <v>325</v>
       </c>
       <c r="U229" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V229" t="n">
         <v>46.16531</v>
@@ -16468,7 +16468,7 @@
         <v>325</v>
       </c>
       <c r="U230" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V230" t="n">
         <v>46.18336</v>
@@ -16538,7 +16538,7 @@
         <v>325</v>
       </c>
       <c r="U231" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V231" t="n">
         <v>46.18337</v>
@@ -16608,7 +16608,7 @@
         <v>325</v>
       </c>
       <c r="U232" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V232" t="n">
         <v>46.13115</v>
@@ -16678,7 +16678,7 @@
         <v>325</v>
       </c>
       <c r="U233" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V233" t="n">
         <v>46.20087</v>
@@ -16748,7 +16748,7 @@
         <v>325</v>
       </c>
       <c r="U234" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V234" t="n">
         <v>46.1967</v>
@@ -16818,7 +16818,7 @@
         <v>325</v>
       </c>
       <c r="U235" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V235" t="n">
         <v>45.22975</v>
@@ -16888,7 +16888,7 @@
         <v>325</v>
       </c>
       <c r="U236" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V236" t="n">
         <v>46.24836</v>
@@ -16958,7 +16958,7 @@
         <v>325</v>
       </c>
       <c r="U237" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V237" t="n">
         <v>46.23059</v>
@@ -17028,7 +17028,7 @@
         <v>250</v>
       </c>
       <c r="U238" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V238" t="n">
         <v>46.00308</v>
@@ -17098,7 +17098,7 @@
         <v>325</v>
       </c>
       <c r="U239" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V239" t="n">
         <v>46.04614</v>
@@ -17168,7 +17168,7 @@
         <v>325</v>
       </c>
       <c r="U240" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V240" t="n">
         <v>46.07142</v>
@@ -17238,7 +17238,7 @@
         <v>325</v>
       </c>
       <c r="U241" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V241" t="n">
         <v>46.80475</v>
@@ -17308,7 +17308,7 @@
         <v>325</v>
       </c>
       <c r="U242" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V242" t="n">
         <v>46.55781</v>
@@ -17378,7 +17378,7 @@
         <v>325</v>
       </c>
       <c r="U243" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V243" t="n">
         <v>46.59105</v>
@@ -17448,7 +17448,7 @@
         <v>325</v>
       </c>
       <c r="U244" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V244" t="n">
         <v>46.50336</v>
@@ -17518,7 +17518,7 @@
         <v>325</v>
       </c>
       <c r="U245" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V245" t="n">
         <v>46.54614</v>
@@ -17588,7 +17588,7 @@
         <v>325</v>
       </c>
       <c r="U246" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V246" t="n">
         <v>46.53503</v>
@@ -17658,7 +17658,7 @@
         <v>325</v>
       </c>
       <c r="U247" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V247" t="n">
         <v>46.64475</v>
@@ -17728,7 +17728,7 @@
         <v>325</v>
       </c>
       <c r="U248" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V248" t="n">
         <v>46.71948</v>
@@ -17798,7 +17798,7 @@
         <v>325</v>
       </c>
       <c r="U249" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V249" t="n">
         <v>46.67503</v>
@@ -17868,7 +17868,7 @@
         <v>325</v>
       </c>
       <c r="U250" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V250" t="n">
         <v>46.70447</v>
@@ -17938,7 +17938,7 @@
         <v>325</v>
       </c>
       <c r="U251" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V251" t="n">
         <v>46.7167</v>
@@ -18008,7 +18008,7 @@
         <v>325</v>
       </c>
       <c r="U252" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V252" t="n">
         <v>46.73837</v>
@@ -18078,7 +18078,7 @@
         <v>325</v>
       </c>
       <c r="U253" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V253" t="n">
         <v>46.53198</v>
@@ -18148,7 +18148,7 @@
         <v>325</v>
       </c>
       <c r="U254" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V254" t="n">
         <v>46.6678</v>
@@ -18218,7 +18218,7 @@
         <v>325</v>
       </c>
       <c r="U255" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V255" t="n">
         <v>46.54169</v>
@@ -18288,7 +18288,7 @@
         <v>325</v>
       </c>
       <c r="U256" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V256" t="n">
         <v>46.54086</v>
@@ -18358,7 +18358,7 @@
         <v>325</v>
       </c>
       <c r="U257" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V257" t="n">
         <v>46.67336</v>
@@ -18428,7 +18428,7 @@
         <v>325</v>
       </c>
       <c r="U258" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V258" t="n">
         <v>46.74363</v>
@@ -18498,7 +18498,7 @@
         <v>325</v>
       </c>
       <c r="U259" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V259" t="n">
         <v>46.57614</v>
@@ -18568,7 +18568,7 @@
         <v>325</v>
       </c>
       <c r="U260" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V260" t="n">
         <v>46.66141</v>
@@ -18638,7 +18638,7 @@
         <v>325</v>
       </c>
       <c r="U261" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V261" t="n">
         <v>46.58056</v>
@@ -18708,7 +18708,7 @@
         <v>325</v>
       </c>
       <c r="U262" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V262" t="n">
         <v>46.64918</v>
@@ -18778,7 +18778,7 @@
         <v>325</v>
       </c>
       <c r="U263" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V263" t="n">
         <v>44.89056</v>
@@ -18848,7 +18848,7 @@
         <v>325</v>
       </c>
       <c r="U264" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V264" t="n">
         <v>45.01195</v>
@@ -18918,7 +18918,7 @@
         <v>325</v>
       </c>
       <c r="U265" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V265" t="n">
         <v>45.06529</v>
@@ -18984,7 +18984,7 @@
         <v>325</v>
       </c>
       <c r="U266" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V266" t="n">
         <v>47.71058</v>
@@ -19054,7 +19054,7 @@
         <v>325</v>
       </c>
       <c r="U267" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V267" t="n">
         <v>45.44224</v>
@@ -19084,7 +19084,7 @@
       <c r="E268" t="inlineStr"/>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
@@ -19124,7 +19124,7 @@
         <v>325</v>
       </c>
       <c r="U268" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V268" t="n">
         <v>45.7142</v>
@@ -19194,7 +19194,7 @@
         <v>325</v>
       </c>
       <c r="U269" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V269" t="n">
         <v>46.64364</v>
@@ -19264,7 +19264,7 @@
         <v>325</v>
       </c>
       <c r="U270" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V270" t="n">
         <v>46.80392</v>
@@ -19334,7 +19334,7 @@
         <v>325</v>
       </c>
       <c r="U271" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V271" t="n">
         <v>46.7492</v>
@@ -19404,7 +19404,7 @@
         <v>325</v>
       </c>
       <c r="U272" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V272" t="n">
         <v>46.23892</v>
@@ -19474,7 +19474,7 @@
         <v>325</v>
       </c>
       <c r="U273" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V273" t="n">
         <v>46.01558</v>
@@ -19544,7 +19544,7 @@
         <v>325</v>
       </c>
       <c r="U274" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V274" t="n">
         <v>45.26363</v>
@@ -19614,7 +19614,7 @@
         <v>325</v>
       </c>
       <c r="U275" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V275" t="n">
         <v>45.43113</v>
@@ -19684,7 +19684,7 @@
         <v>325</v>
       </c>
       <c r="U276" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V276" t="n">
         <v>45.39502</v>
@@ -19754,7 +19754,7 @@
         <v>325</v>
       </c>
       <c r="U277" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V277" t="n">
         <v>45.39252</v>
@@ -19824,7 +19824,7 @@
         <v>325</v>
       </c>
       <c r="U278" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V278" t="n">
         <v>45.46835</v>
@@ -19894,7 +19894,7 @@
         <v>325</v>
       </c>
       <c r="U279" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V279" t="n">
         <v>46.01808</v>
@@ -19964,7 +19964,7 @@
         <v>325</v>
       </c>
       <c r="U280" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V280" t="n">
         <v>45.38835</v>
@@ -20034,7 +20034,7 @@
         <v>325</v>
       </c>
       <c r="U281" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V281" t="n">
         <v>45.48947</v>
@@ -20104,7 +20104,7 @@
         <v>325</v>
       </c>
       <c r="U282" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V282" t="n">
         <v>45.44113</v>
@@ -20174,7 +20174,7 @@
         <v>325</v>
       </c>
       <c r="U283" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V283" t="n">
         <v>45.41724</v>
@@ -20244,7 +20244,7 @@
         <v>325</v>
       </c>
       <c r="U284" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V284" t="n">
         <v>45.3978</v>
@@ -20314,7 +20314,7 @@
         <v>325</v>
       </c>
       <c r="U285" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V285" t="n">
         <v>45.35142</v>
@@ -20384,7 +20384,7 @@
         <v>325</v>
       </c>
       <c r="U286" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V286" t="n">
         <v>45.3028</v>
@@ -20454,7 +20454,7 @@
         <v>325</v>
       </c>
       <c r="U287" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V287" t="n">
         <v>45.39141</v>
@@ -20524,7 +20524,7 @@
         <v>325</v>
       </c>
       <c r="U288" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V288" t="n">
         <v>45.45836</v>
@@ -20594,7 +20594,7 @@
         <v>325</v>
       </c>
       <c r="U289" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V289" t="n">
         <v>45.32142</v>
@@ -20664,7 +20664,7 @@
         <v>300</v>
       </c>
       <c r="U290" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V290" t="n">
         <v>45.46364</v>
@@ -20734,7 +20734,7 @@
         <v>325</v>
       </c>
       <c r="U291" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V291" t="n">
         <v>45.48336</v>
@@ -20804,7 +20804,7 @@
         <v>325</v>
       </c>
       <c r="U292" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V292" t="n">
         <v>45.50001</v>
@@ -20874,7 +20874,7 @@
         <v>325</v>
       </c>
       <c r="U293" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V293" t="n">
         <v>45.26808</v>
@@ -20944,7 +20944,7 @@
         <v>325</v>
       </c>
       <c r="U294" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V294" t="n">
         <v>45.40363</v>
@@ -21014,7 +21014,7 @@
         <v>325</v>
       </c>
       <c r="U295" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V295" t="n">
         <v>45.41086</v>
@@ -21084,7 +21084,7 @@
         <v>225</v>
       </c>
       <c r="U296" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V296" t="n">
         <v>45.46668</v>
@@ -21154,7 +21154,7 @@
         <v>325</v>
       </c>
       <c r="U297" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V297" t="n">
         <v>45.4328</v>
@@ -21224,7 +21224,7 @@
         <v>325</v>
       </c>
       <c r="U298" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V298" t="n">
         <v>45.45308</v>
@@ -21294,7 +21294,7 @@
         <v>325</v>
       </c>
       <c r="U299" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V299" t="n">
         <v>45.4678</v>
@@ -21364,7 +21364,7 @@
         <v>325</v>
       </c>
       <c r="U300" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V300" t="n">
         <v>45.41891</v>
@@ -21434,7 +21434,7 @@
         <v>325</v>
       </c>
       <c r="U301" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V301" t="n">
         <v>45.45447</v>
@@ -21504,7 +21504,7 @@
         <v>325</v>
       </c>
       <c r="U302" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V302" t="n">
         <v>45.47086</v>
@@ -21574,7 +21574,7 @@
         <v>325</v>
       </c>
       <c r="U303" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V303" t="n">
         <v>45.4114</v>
@@ -21644,7 +21644,7 @@
         <v>325</v>
       </c>
       <c r="U304" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V304" t="n">
         <v>45.38449</v>
@@ -21714,7 +21714,7 @@
         <v>325</v>
       </c>
       <c r="U305" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V305" t="n">
         <v>45.42169</v>
@@ -21784,7 +21784,7 @@
         <v>325</v>
       </c>
       <c r="U306" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V306" t="n">
         <v>45.30919</v>
@@ -21854,7 +21854,7 @@
         <v>250</v>
       </c>
       <c r="U307" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V307" t="n">
         <v>45.31502</v>
@@ -21924,7 +21924,7 @@
         <v>325</v>
       </c>
       <c r="U308" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V308" t="n">
         <v>45.39975</v>
@@ -21994,7 +21994,7 @@
         <v>325</v>
       </c>
       <c r="U309" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V309" t="n">
         <v>45.27975</v>
@@ -22064,7 +22064,7 @@
         <v>325</v>
       </c>
       <c r="U310" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V310" t="n">
         <v>45.28197</v>
@@ -22134,7 +22134,7 @@
         <v>325</v>
       </c>
       <c r="U311" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V311" t="n">
         <v>45.4203</v>
@@ -22204,7 +22204,7 @@
         <v>325</v>
       </c>
       <c r="U312" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V312" t="n">
         <v>45.35863</v>
@@ -22274,7 +22274,7 @@
         <v>325</v>
       </c>
       <c r="U313" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V313" t="n">
         <v>45.33086</v>
@@ -22344,7 +22344,7 @@
         <v>325</v>
       </c>
       <c r="U314" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V314" t="n">
         <v>45.20448</v>
@@ -22414,7 +22414,7 @@
         <v>325</v>
       </c>
       <c r="U315" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V315" t="n">
         <v>45.31669</v>
@@ -22444,7 +22444,7 @@
       <c r="E316" t="inlineStr"/>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Rare earths</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
@@ -22484,7 +22484,7 @@
         <v>325</v>
       </c>
       <c r="U316" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V316" t="n">
         <v>45.48419</v>
@@ -22554,7 +22554,7 @@
         <v>325</v>
       </c>
       <c r="U317" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V317" t="n">
         <v>45.49642</v>
@@ -22624,7 +22624,7 @@
         <v>325</v>
       </c>
       <c r="U318" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V318" t="n">
         <v>45.2742</v>
@@ -22690,7 +22690,7 @@
         <v>325</v>
       </c>
       <c r="U319" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V319" t="n">
         <v>47.44808</v>
@@ -22760,7 +22760,7 @@
         <v>325</v>
       </c>
       <c r="U320" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V320" t="n">
         <v>47.80605</v>
@@ -22826,7 +22826,7 @@
         <v>300</v>
       </c>
       <c r="U321" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V321" t="n">
         <v>48.01198</v>
@@ -22892,7 +22892,7 @@
         <v>325</v>
       </c>
       <c r="U322" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V322" t="n">
         <v>47.30226</v>
@@ -22962,7 +22962,7 @@
         <v>325</v>
       </c>
       <c r="U323" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V323" t="n">
         <v>45.52002</v>
@@ -23032,7 +23032,7 @@
         <v>300</v>
       </c>
       <c r="U324" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V324" t="n">
         <v>45.58694</v>
@@ -23102,7 +23102,7 @@
         <v>325</v>
       </c>
       <c r="U325" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V325" t="n">
         <v>45.53473</v>
@@ -23172,7 +23172,7 @@
         <v>325</v>
       </c>
       <c r="U326" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V326" t="n">
         <v>45.64613</v>
@@ -23242,7 +23242,7 @@
         <v>325</v>
       </c>
       <c r="U327" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V327" t="n">
         <v>45.57058</v>
@@ -23312,7 +23312,7 @@
         <v>325</v>
       </c>
       <c r="U328" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V328" t="n">
         <v>45.66889</v>
@@ -23382,7 +23382,7 @@
         <v>325</v>
       </c>
       <c r="U329" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V329" t="n">
         <v>45.55003</v>
@@ -23452,7 +23452,7 @@
         <v>300</v>
       </c>
       <c r="U330" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V330" t="n">
         <v>45.60947</v>
@@ -23522,7 +23522,7 @@
         <v>250</v>
       </c>
       <c r="U331" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V331" t="n">
         <v>45.65142</v>
@@ -23592,7 +23592,7 @@
         <v>325</v>
       </c>
       <c r="U332" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V332" t="n">
         <v>46.60003</v>
@@ -23662,7 +23662,7 @@
         <v>325</v>
       </c>
       <c r="U333" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V333" t="n">
         <v>46.6217</v>
@@ -23732,7 +23732,7 @@
         <v>325</v>
       </c>
       <c r="U334" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V334" t="n">
         <v>46.69698</v>
@@ -23802,7 +23802,7 @@
         <v>325</v>
       </c>
       <c r="U335" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V335" t="n">
         <v>46.59753</v>
@@ -23872,7 +23872,7 @@
         <v>325</v>
       </c>
       <c r="U336" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V336" t="n">
         <v>46.64253</v>
@@ -23938,7 +23938,7 @@
         <v>325</v>
       </c>
       <c r="U337" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V337" t="n">
         <v>46.64308</v>
@@ -24008,7 +24008,7 @@
         <v>325</v>
       </c>
       <c r="U338" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V338" t="n">
         <v>46.57113</v>
@@ -24078,7 +24078,7 @@
         <v>325</v>
       </c>
       <c r="U339" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V339" t="n">
         <v>46.56753</v>
@@ -24148,7 +24148,7 @@
         <v>325</v>
       </c>
       <c r="U340" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V340" t="n">
         <v>46.57086</v>
@@ -24218,7 +24218,7 @@
         <v>325</v>
       </c>
       <c r="U341" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V341" t="n">
         <v>46.58559</v>
@@ -24288,7 +24288,7 @@
         <v>325</v>
       </c>
       <c r="U342" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V342" t="n">
         <v>46.5817</v>
@@ -24358,7 +24358,7 @@
         <v>325</v>
       </c>
       <c r="U343" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V343" t="n">
         <v>46.55446</v>
@@ -24428,7 +24428,7 @@
         <v>325</v>
       </c>
       <c r="U344" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V344" t="n">
         <v>46.65031</v>
@@ -24498,7 +24498,7 @@
         <v>325</v>
       </c>
       <c r="U345" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V345" t="n">
         <v>46.52224</v>
@@ -24568,7 +24568,7 @@
         <v>325</v>
       </c>
       <c r="U346" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V346" t="n">
         <v>47.66323</v>
@@ -24638,7 +24638,7 @@
         <v>325</v>
       </c>
       <c r="U347" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V347" t="n">
         <v>47.65736</v>
@@ -24708,7 +24708,7 @@
         <v>325</v>
       </c>
       <c r="U348" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V348" t="n">
         <v>47.67912</v>
@@ -24778,7 +24778,7 @@
         <v>325</v>
       </c>
       <c r="U349" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V349" t="n">
         <v>47.69524</v>
@@ -24848,7 +24848,7 @@
         <v>325</v>
       </c>
       <c r="U350" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V350" t="n">
         <v>47.67587</v>
@@ -24918,7 +24918,7 @@
         <v>325</v>
       </c>
       <c r="U351" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V351" t="n">
         <v>47.68002</v>
@@ -24984,7 +24984,7 @@
         <v>325</v>
       </c>
       <c r="U352" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V352" t="n">
         <v>47.57781</v>
@@ -25050,7 +25050,7 @@
         <v>325</v>
       </c>
       <c r="U353" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V353" t="n">
         <v>47.58503</v>
@@ -25120,7 +25120,7 @@
         <v>325</v>
       </c>
       <c r="U354" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V354" t="n">
         <v>47.68499</v>
@@ -25190,7 +25190,7 @@
         <v>325</v>
       </c>
       <c r="U355" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V355" t="n">
         <v>47.67864</v>
@@ -25260,7 +25260,7 @@
         <v>325</v>
       </c>
       <c r="U356" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V356" t="n">
         <v>47.6782</v>
@@ -25326,7 +25326,7 @@
         <v>325</v>
       </c>
       <c r="U357" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V357" t="n">
         <v>47.67253</v>
@@ -25392,7 +25392,7 @@
         <v>325</v>
       </c>
       <c r="U358" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V358" t="n">
         <v>47.6903</v>
@@ -25462,7 +25462,7 @@
         <v>325</v>
       </c>
       <c r="U359" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V359" t="n">
         <v>47.69142</v>
@@ -25528,7 +25528,7 @@
         <v>325</v>
       </c>
       <c r="U360" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V360" t="n">
         <v>47.68615</v>
@@ -25598,7 +25598,7 @@
         <v>325</v>
       </c>
       <c r="U361" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V361" t="n">
         <v>47.68273</v>
@@ -25668,7 +25668,7 @@
         <v>300</v>
       </c>
       <c r="U362" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V362" t="n">
         <v>47.73364</v>
@@ -25738,7 +25738,7 @@
         <v>325</v>
       </c>
       <c r="U363" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V363" t="n">
         <v>47.70062</v>
@@ -25808,7 +25808,7 @@
         <v>325</v>
       </c>
       <c r="U364" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V364" t="n">
         <v>47.69378</v>
@@ -25878,7 +25878,7 @@
         <v>325</v>
       </c>
       <c r="U365" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V365" t="n">
         <v>47.72173</v>
@@ -25944,7 +25944,7 @@
         <v>325</v>
       </c>
       <c r="U366" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V366" t="n">
         <v>47.73782</v>
@@ -26010,7 +26010,7 @@
         <v>325</v>
       </c>
       <c r="U367" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V367" t="n">
         <v>47.56337</v>
@@ -26080,7 +26080,7 @@
         <v>325</v>
       </c>
       <c r="U368" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V368" t="n">
         <v>47.68435</v>
@@ -26146,7 +26146,7 @@
         <v>325</v>
       </c>
       <c r="U369" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V369" t="n">
         <v>47.68087</v>
@@ -26216,7 +26216,7 @@
         <v>325</v>
       </c>
       <c r="U370" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V370" t="n">
         <v>47.7067</v>
@@ -26286,7 +26286,7 @@
         <v>325</v>
       </c>
       <c r="U371" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V371" t="n">
         <v>47.71145</v>
@@ -26356,7 +26356,7 @@
         <v>325</v>
       </c>
       <c r="U372" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V372" t="n">
         <v>47.62447</v>
@@ -26426,7 +26426,7 @@
         <v>325</v>
       </c>
       <c r="U373" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V373" t="n">
         <v>47.68907</v>
@@ -26496,7 +26496,7 @@
         <v>325</v>
       </c>
       <c r="U374" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V374" t="n">
         <v>47.69025</v>
@@ -26566,7 +26566,7 @@
         <v>325</v>
       </c>
       <c r="U375" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V375" t="n">
         <v>47.7016</v>
@@ -26636,7 +26636,7 @@
         <v>325</v>
       </c>
       <c r="U376" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V376" t="n">
         <v>47.71186</v>
@@ -26706,7 +26706,7 @@
         <v>325</v>
       </c>
       <c r="U377" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V377" t="n">
         <v>47.68699</v>
@@ -26772,7 +26772,7 @@
         <v>325</v>
       </c>
       <c r="U378" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V378" t="n">
         <v>47.4478</v>
@@ -26838,7 +26838,7 @@
         <v>325</v>
       </c>
       <c r="U379" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V379" t="n">
         <v>47.32835</v>
@@ -26908,7 +26908,7 @@
         <v>325</v>
       </c>
       <c r="U380" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V380" t="n">
         <v>47.77065</v>
@@ -26974,7 +26974,7 @@
         <v>325</v>
       </c>
       <c r="U381" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V381" t="n">
         <v>47.75336</v>
@@ -27040,7 +27040,7 @@
         <v>325</v>
       </c>
       <c r="U382" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V382" t="n">
         <v>47.76704</v>
@@ -27110,7 +27110,7 @@
         <v>325</v>
       </c>
       <c r="U383" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V383" t="n">
         <v>47.84586</v>
@@ -27180,7 +27180,7 @@
         <v>300</v>
       </c>
       <c r="U384" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V384" t="n">
         <v>47.66975</v>
@@ -27250,7 +27250,7 @@
         <v>325</v>
       </c>
       <c r="U385" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V385" t="n">
         <v>47.68623</v>
@@ -27316,7 +27316,7 @@
         <v>325</v>
       </c>
       <c r="U386" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V386" t="n">
         <v>47.53947</v>
@@ -27386,7 +27386,7 @@
         <v>325</v>
       </c>
       <c r="U387" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V387" t="n">
         <v>47.51448</v>
@@ -27456,7 +27456,7 @@
         <v>325</v>
       </c>
       <c r="U388" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V388" t="n">
         <v>47.25975</v>
@@ -27526,7 +27526,7 @@
         <v>325</v>
       </c>
       <c r="U389" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V389" t="n">
         <v>47.84976</v>
@@ -27596,7 +27596,7 @@
         <v>325</v>
       </c>
       <c r="U390" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V390" t="n">
         <v>47.85504</v>
@@ -27666,7 +27666,7 @@
         <v>175</v>
       </c>
       <c r="U391" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V391" t="n">
         <v>47.56614</v>
@@ -27736,7 +27736,7 @@
         <v>325</v>
       </c>
       <c r="U392" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V392" t="n">
         <v>47.74169</v>
@@ -27806,7 +27806,7 @@
         <v>325</v>
       </c>
       <c r="U393" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V393" t="n">
         <v>45.66865</v>
@@ -27876,7 +27876,7 @@
         <v>325</v>
       </c>
       <c r="U394" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V394" t="n">
         <v>47.07836</v>
@@ -27946,7 +27946,7 @@
         <v>325</v>
       </c>
       <c r="U395" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V395" t="n">
         <v>47.02281</v>
@@ -28016,7 +28016,7 @@
         <v>325</v>
       </c>
       <c r="U396" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V396" t="n">
         <v>47.09781</v>
@@ -28086,7 +28086,7 @@
         <v>325</v>
       </c>
       <c r="U397" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V397" t="n">
         <v>47.16447</v>
@@ -28156,7 +28156,7 @@
         <v>325</v>
       </c>
       <c r="U398" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V398" t="n">
         <v>47.14114</v>
@@ -28222,7 +28222,7 @@
         <v>300</v>
       </c>
       <c r="U399" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V399" t="n">
         <v>47.23114</v>
@@ -28292,7 +28292,7 @@
         <v>325</v>
       </c>
       <c r="U400" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V400" t="n">
         <v>47.71257</v>
@@ -28358,7 +28358,7 @@
         <v>325</v>
       </c>
       <c r="U401" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V401" t="n">
         <v>47.34391</v>
@@ -28424,7 +28424,7 @@
         <v>325</v>
       </c>
       <c r="U402" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V402" t="n">
         <v>47.86281</v>
@@ -28494,7 +28494,7 @@
         <v>325</v>
       </c>
       <c r="U403" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V403" t="n">
         <v>47.51779</v>
@@ -28560,7 +28560,7 @@
         <v>325</v>
       </c>
       <c r="U404" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V404" t="n">
         <v>47.6667</v>
@@ -28630,7 +28630,7 @@
         <v>325</v>
       </c>
       <c r="U405" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V405" t="n">
         <v>47.65726</v>
@@ -28700,7 +28700,7 @@
         <v>325</v>
       </c>
       <c r="U406" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V406" t="n">
         <v>46.60503</v>
@@ -28766,7 +28766,7 @@
         <v>325</v>
       </c>
       <c r="U407" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V407" t="n">
         <v>46.66503</v>
@@ -28832,7 +28832,7 @@
         <v>325</v>
       </c>
       <c r="U408" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V408" t="n">
         <v>46.66531</v>
@@ -28898,7 +28898,7 @@
         <v>325</v>
       </c>
       <c r="U409" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V409" t="n">
         <v>46.66475</v>
@@ -28968,7 +28968,7 @@
         <v>325</v>
       </c>
       <c r="U410" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V410" t="n">
         <v>46.61003</v>
@@ -29038,7 +29038,7 @@
         <v>325</v>
       </c>
       <c r="U411" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V411" t="n">
         <v>46.64142</v>
@@ -29108,7 +29108,7 @@
         <v>325</v>
       </c>
       <c r="U412" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V412" t="n">
         <v>46.6667</v>
@@ -29174,7 +29174,7 @@
         <v>325</v>
       </c>
       <c r="U413" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V413" t="n">
         <v>46.6778</v>
@@ -29240,7 +29240,7 @@
         <v>325</v>
       </c>
       <c r="U414" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V414" t="n">
         <v>46.66308</v>
@@ -29310,7 +29310,7 @@
         <v>325</v>
       </c>
       <c r="U415" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V415" t="n">
         <v>46.71364</v>
@@ -29380,7 +29380,7 @@
         <v>325</v>
       </c>
       <c r="U416" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V416" t="n">
         <v>45.25642</v>
@@ -29450,7 +29450,7 @@
         <v>325</v>
       </c>
       <c r="U417" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V417" t="n">
         <v>45.70142</v>
@@ -29520,7 +29520,7 @@
         <v>325</v>
       </c>
       <c r="U418" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V418" t="n">
         <v>45.72697</v>
@@ -29590,7 +29590,7 @@
         <v>325</v>
       </c>
       <c r="U419" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V419" t="n">
         <v>45.70586</v>
@@ -29660,7 +29660,7 @@
         <v>325</v>
       </c>
       <c r="U420" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V420" t="n">
         <v>45.72726</v>
@@ -29730,7 +29730,7 @@
         <v>325</v>
       </c>
       <c r="U421" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V421" t="n">
         <v>45.53197</v>
@@ -29800,7 +29800,7 @@
         <v>325</v>
       </c>
       <c r="U422" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V422" t="n">
         <v>45.68695</v>
@@ -29870,7 +29870,7 @@
         <v>325</v>
       </c>
       <c r="U423" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V423" t="n">
         <v>45.6928</v>
@@ -29940,7 +29940,7 @@
         <v>300</v>
       </c>
       <c r="U424" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V424" t="n">
         <v>47.17808</v>
@@ -30006,7 +30006,7 @@
         <v>325</v>
       </c>
       <c r="U425" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V425" t="n">
         <v>47.27281</v>
@@ -30072,7 +30072,7 @@
         <v>325</v>
       </c>
       <c r="U426" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V426" t="n">
         <v>47.81002</v>
@@ -30142,7 +30142,7 @@
         <v>325</v>
       </c>
       <c r="U427" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V427" t="n">
         <v>45.95642</v>
@@ -30212,7 +30212,7 @@
         <v>325</v>
       </c>
       <c r="U428" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V428" t="n">
         <v>45.8978</v>
@@ -30282,7 +30282,7 @@
         <v>325</v>
       </c>
       <c r="U429" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V429" t="n">
         <v>45.5739</v>
@@ -30352,7 +30352,7 @@
         <v>325</v>
       </c>
       <c r="U430" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V430" t="n">
         <v>45.98392</v>
@@ -30422,7 +30422,7 @@
         <v>325</v>
       </c>
       <c r="U431" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V431" t="n">
         <v>45.97418</v>
@@ -30492,7 +30492,7 @@
         <v>325</v>
       </c>
       <c r="U432" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V432" t="n">
         <v>45.95029</v>
@@ -30562,7 +30562,7 @@
         <v>325</v>
       </c>
       <c r="U433" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V433" t="n">
         <v>45.93559</v>
@@ -30632,7 +30632,7 @@
         <v>300</v>
       </c>
       <c r="U434" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V434" t="n">
         <v>45.98948</v>
@@ -30702,7 +30702,7 @@
         <v>325</v>
       </c>
       <c r="U435" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V435" t="n">
         <v>45.93114</v>
@@ -30772,7 +30772,7 @@
         <v>325</v>
       </c>
       <c r="U436" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V436" t="n">
         <v>45.86198</v>
@@ -30842,7 +30842,7 @@
         <v>325</v>
       </c>
       <c r="U437" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V437" t="n">
         <v>45.19781</v>
@@ -30912,7 +30912,7 @@
         <v>325</v>
       </c>
       <c r="U438" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V438" t="n">
         <v>45.17614</v>
@@ -30982,7 +30982,7 @@
         <v>325</v>
       </c>
       <c r="U439" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V439" t="n">
         <v>45.18336</v>
@@ -31052,7 +31052,7 @@
         <v>325</v>
       </c>
       <c r="U440" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V440" t="n">
         <v>45.17947</v>
@@ -31122,7 +31122,7 @@
         <v>325</v>
       </c>
       <c r="U441" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V441" t="n">
         <v>45.16891</v>
@@ -31192,7 +31192,7 @@
         <v>325</v>
       </c>
       <c r="U442" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V442" t="n">
         <v>45.14114</v>
@@ -31262,7 +31262,7 @@
         <v>325</v>
       </c>
       <c r="U443" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V443" t="n">
         <v>45.1517</v>
@@ -31332,7 +31332,7 @@
         <v>325</v>
       </c>
       <c r="U444" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V444" t="n">
         <v>45.19697</v>
@@ -31402,7 +31402,7 @@
         <v>325</v>
       </c>
       <c r="U445" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V445" t="n">
         <v>45.08586</v>
@@ -31472,7 +31472,7 @@
         <v>325</v>
       </c>
       <c r="U446" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V446" t="n">
         <v>45.2453</v>
@@ -31542,7 +31542,7 @@
         <v>325</v>
       </c>
       <c r="U447" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V447" t="n">
         <v>45.67613</v>
@@ -31612,7 +31612,7 @@
         <v>325</v>
       </c>
       <c r="U448" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V448" t="n">
         <v>45.67836</v>
@@ -31682,7 +31682,7 @@
         <v>325</v>
       </c>
       <c r="U449" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V449" t="n">
         <v>45.71696</v>
@@ -31752,7 +31752,7 @@
         <v>325</v>
       </c>
       <c r="U450" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V450" t="n">
         <v>45.73919</v>
@@ -31818,7 +31818,7 @@
         <v>325</v>
       </c>
       <c r="U451" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V451" t="n">
         <v>46.84808</v>
@@ -31888,7 +31888,7 @@
         <v>325</v>
       </c>
       <c r="U452" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V452" t="n">
         <v>45.10863</v>
@@ -31958,7 +31958,7 @@
         <v>325</v>
       </c>
       <c r="U453" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V453" t="n">
         <v>45.19363</v>
@@ -32024,7 +32024,7 @@
         <v>325</v>
       </c>
       <c r="U454" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V454" t="n">
         <v>46.9742</v>
@@ -32094,7 +32094,7 @@
         <v>325</v>
       </c>
       <c r="U455" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V455" t="n">
         <v>46.75282</v>
@@ -32164,7 +32164,7 @@
         <v>325</v>
       </c>
       <c r="U456" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V456" t="n">
         <v>46.77503</v>
@@ -32230,7 +32230,7 @@
         <v>325</v>
       </c>
       <c r="U457" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V457" t="n">
         <v>46.93142</v>
@@ -32300,7 +32300,7 @@
         <v>325</v>
       </c>
       <c r="U458" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V458" t="n">
         <v>45.20531</v>
@@ -32370,7 +32370,7 @@
         <v>325</v>
       </c>
       <c r="U459" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V459" t="n">
         <v>45.15781</v>
@@ -32440,7 +32440,7 @@
         <v>325</v>
       </c>
       <c r="U460" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V460" t="n">
         <v>45.14808</v>
@@ -32510,7 +32510,7 @@
         <v>325</v>
       </c>
       <c r="U461" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V461" t="n">
         <v>45.1403</v>
@@ -32580,7 +32580,7 @@
         <v>325</v>
       </c>
       <c r="U462" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V462" t="n">
         <v>45.1128</v>
@@ -32650,7 +32650,7 @@
         <v>325</v>
       </c>
       <c r="U463" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V463" t="n">
         <v>45.11087</v>
@@ -32720,7 +32720,7 @@
         <v>325</v>
       </c>
       <c r="U464" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V464" t="n">
         <v>45.09503</v>
@@ -32790,7 +32790,7 @@
         <v>325</v>
       </c>
       <c r="U465" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V465" t="n">
         <v>45.2353</v>
@@ -32860,7 +32860,7 @@
         <v>325</v>
       </c>
       <c r="U466" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V466" t="n">
         <v>45.12891</v>
@@ -32930,7 +32930,7 @@
         <v>325</v>
       </c>
       <c r="U467" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V467" t="n">
         <v>45.13058</v>
@@ -33000,7 +33000,7 @@
         <v>325</v>
       </c>
       <c r="U468" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V468" t="n">
         <v>45.16641</v>
@@ -33070,7 +33070,7 @@
         <v>325</v>
       </c>
       <c r="U469" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V469" t="n">
         <v>45.14309</v>
@@ -33140,7 +33140,7 @@
         <v>325</v>
       </c>
       <c r="U470" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V470" t="n">
         <v>45.15697</v>
@@ -33210,7 +33210,7 @@
         <v>325</v>
       </c>
       <c r="U471" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V471" t="n">
         <v>45.14058</v>
@@ -33280,7 +33280,7 @@
         <v>325</v>
       </c>
       <c r="U472" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V472" t="n">
         <v>45.06031</v>
@@ -33350,7 +33350,7 @@
         <v>325</v>
       </c>
       <c r="U473" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V473" t="n">
         <v>45.06697</v>
@@ -33420,7 +33420,7 @@
         <v>325</v>
       </c>
       <c r="U474" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V474" t="n">
         <v>45.08475</v>
@@ -33490,7 +33490,7 @@
         <v>325</v>
       </c>
       <c r="U475" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V475" t="n">
         <v>45.12864</v>
@@ -33560,7 +33560,7 @@
         <v>325</v>
       </c>
       <c r="U476" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V476" t="n">
         <v>45.12918</v>
@@ -33630,7 +33630,7 @@
         <v>325</v>
       </c>
       <c r="U477" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V477" t="n">
         <v>45.09808</v>
@@ -33700,7 +33700,7 @@
         <v>325</v>
       </c>
       <c r="U478" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V478" t="n">
         <v>45.09225</v>
@@ -33770,7 +33770,7 @@
         <v>325</v>
       </c>
       <c r="U479" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V479" t="n">
         <v>46.88187</v>
@@ -33836,7 +33836,7 @@
         <v>325</v>
       </c>
       <c r="U480" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V480" t="n">
         <v>46.75198</v>
@@ -33906,7 +33906,7 @@
         <v>325</v>
       </c>
       <c r="U481" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V481" t="n">
         <v>45.12114</v>
@@ -33976,7 +33976,7 @@
         <v>325</v>
       </c>
       <c r="U482" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V482" t="n">
         <v>45.22336</v>
@@ -34046,7 +34046,7 @@
         <v>325</v>
       </c>
       <c r="U483" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V483" t="n">
         <v>45.23529</v>
@@ -34116,7 +34116,7 @@
         <v>325</v>
       </c>
       <c r="U484" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V484" t="n">
         <v>45.08253</v>
@@ -34186,7 +34186,7 @@
         <v>325</v>
       </c>
       <c r="U485" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V485" t="n">
         <v>45.16973</v>
@@ -34256,7 +34256,7 @@
         <v>325</v>
       </c>
       <c r="U486" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V486" t="n">
         <v>45.15336</v>
@@ -34326,7 +34326,7 @@
         <v>325</v>
       </c>
       <c r="U487" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V487" t="n">
         <v>46.93087</v>
@@ -34392,7 +34392,7 @@
         <v>325</v>
       </c>
       <c r="U488" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V488" t="n">
         <v>46.98919</v>
@@ -34462,7 +34462,7 @@
         <v>325</v>
       </c>
       <c r="U489" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V489" t="n">
         <v>45.24753</v>
@@ -34532,7 +34532,7 @@
         <v>325</v>
       </c>
       <c r="U490" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V490" t="n">
         <v>45.16975</v>
@@ -34602,7 +34602,7 @@
         <v>250</v>
       </c>
       <c r="U491" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V491" t="n">
         <v>45.00418</v>
@@ -34672,7 +34672,7 @@
         <v>325</v>
       </c>
       <c r="U492" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V492" t="n">
         <v>45.42058</v>
@@ -34742,7 +34742,7 @@
         <v>325</v>
       </c>
       <c r="U493" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V493" t="n">
         <v>45.15364</v>
@@ -34812,7 +34812,7 @@
         <v>325</v>
       </c>
       <c r="U494" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V494" t="n">
         <v>45.13609</v>
@@ -34882,7 +34882,7 @@
         <v>325</v>
       </c>
       <c r="U495" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V495" t="n">
         <v>45.14836</v>
@@ -34952,7 +34952,7 @@
         <v>325</v>
       </c>
       <c r="U496" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V496" t="n">
         <v>45.0353</v>
@@ -35022,7 +35022,7 @@
         <v>325</v>
       </c>
       <c r="U497" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V497" t="n">
         <v>45.04225</v>
@@ -35092,7 +35092,7 @@
         <v>325</v>
       </c>
       <c r="U498" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V498" t="n">
         <v>45.07669</v>
@@ -35162,7 +35162,7 @@
         <v>325</v>
       </c>
       <c r="U499" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V499" t="n">
         <v>45.08058</v>
@@ -35232,7 +35232,7 @@
         <v>325</v>
       </c>
       <c r="U500" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V500" t="n">
         <v>45.07531</v>
@@ -35302,7 +35302,7 @@
         <v>325</v>
       </c>
       <c r="U501" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V501" t="n">
         <v>45.06808</v>
@@ -35372,7 +35372,7 @@
         <v>325</v>
       </c>
       <c r="U502" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V502" t="n">
         <v>45.0889</v>
@@ -35442,7 +35442,7 @@
         <v>325</v>
       </c>
       <c r="U503" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V503" t="n">
         <v>45.39281</v>
@@ -35512,7 +35512,7 @@
         <v>325</v>
       </c>
       <c r="U504" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V504" t="n">
         <v>45.43698</v>
@@ -35582,7 +35582,7 @@
         <v>325</v>
       </c>
       <c r="U505" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V505" t="n">
         <v>45.38475</v>
@@ -35652,7 +35652,7 @@
         <v>325</v>
       </c>
       <c r="U506" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V506" t="n">
         <v>45.07697</v>
@@ -35722,7 +35722,7 @@
         <v>325</v>
       </c>
       <c r="U507" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V507" t="n">
         <v>46.95281</v>
@@ -35792,7 +35792,7 @@
         <v>325</v>
       </c>
       <c r="U508" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V508" t="n">
         <v>45.44058</v>
@@ -35862,7 +35862,7 @@
         <v>325</v>
       </c>
       <c r="U509" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V509" t="n">
         <v>45.38225</v>
@@ -35932,7 +35932,7 @@
         <v>325</v>
       </c>
       <c r="U510" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V510" t="n">
         <v>46.78809</v>
@@ -35998,7 +35998,7 @@
         <v>325</v>
       </c>
       <c r="U511" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V511" t="n">
         <v>46.91199</v>
@@ -36064,7 +36064,7 @@
         <v>325</v>
       </c>
       <c r="U512" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V512" t="n">
         <v>46.94393</v>
@@ -36134,7 +36134,7 @@
         <v>325</v>
       </c>
       <c r="U513" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V513" t="n">
         <v>46.93727</v>
@@ -36200,7 +36200,7 @@
         <v>325</v>
       </c>
       <c r="U514" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V514" t="n">
         <v>46.95699</v>
@@ -36266,7 +36266,7 @@
         <v>325</v>
       </c>
       <c r="U515" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V515" t="n">
         <v>46.89643</v>
@@ -36332,7 +36332,7 @@
         <v>325</v>
       </c>
       <c r="U516" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V516" t="n">
         <v>46.89476</v>
@@ -36398,7 +36398,7 @@
         <v>325</v>
       </c>
       <c r="U517" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V517" t="n">
         <v>46.91727</v>
@@ -36468,7 +36468,7 @@
         <v>325</v>
       </c>
       <c r="U518" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V518" t="n">
         <v>45.25087</v>
@@ -36538,7 +36538,7 @@
         <v>325</v>
       </c>
       <c r="U519" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V519" t="n">
         <v>45.41337</v>
@@ -36608,7 +36608,7 @@
         <v>325</v>
       </c>
       <c r="U520" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V520" t="n">
         <v>45.19004</v>
@@ -36678,7 +36678,7 @@
         <v>325</v>
       </c>
       <c r="U521" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V521" t="n">
         <v>45.23585</v>
@@ -36748,7 +36748,7 @@
         <v>325</v>
       </c>
       <c r="U522" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V522" t="n">
         <v>45.18504</v>
@@ -36818,7 +36818,7 @@
         <v>325</v>
       </c>
       <c r="U523" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V523" t="n">
         <v>45.58336</v>
@@ -36884,7 +36884,7 @@
         <v>325</v>
       </c>
       <c r="U524" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V524" t="n">
         <v>46.93893</v>
@@ -36954,7 +36954,7 @@
         <v>325</v>
       </c>
       <c r="U525" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V525" t="n">
         <v>45.31474</v>
@@ -37024,7 +37024,7 @@
         <v>325</v>
       </c>
       <c r="U526" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V526" t="n">
         <v>45.31225</v>
@@ -37094,7 +37094,7 @@
         <v>325</v>
       </c>
       <c r="U527" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V527" t="n">
         <v>45.36337</v>
@@ -37164,7 +37164,7 @@
         <v>325</v>
       </c>
       <c r="U528" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V528" t="n">
         <v>45.30614</v>
@@ -37234,7 +37234,7 @@
         <v>325</v>
       </c>
       <c r="U529" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V529" t="n">
         <v>45.30281</v>
@@ -37304,7 +37304,7 @@
         <v>325</v>
       </c>
       <c r="U530" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V530" t="n">
         <v>45.30753</v>
@@ -37374,7 +37374,7 @@
         <v>325</v>
       </c>
       <c r="U531" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V531" t="n">
         <v>45.28254</v>
@@ -37444,7 +37444,7 @@
         <v>325</v>
       </c>
       <c r="U532" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V532" t="n">
         <v>45.58364</v>
@@ -37514,7 +37514,7 @@
         <v>325</v>
       </c>
       <c r="U533" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V533" t="n">
         <v>45.6917</v>
@@ -37584,7 +37584,7 @@
         <v>325</v>
       </c>
       <c r="U534" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V534" t="n">
         <v>45.70726</v>
@@ -37654,7 +37654,7 @@
         <v>325</v>
       </c>
       <c r="U535" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V535" t="n">
         <v>45.7417</v>
@@ -37724,7 +37724,7 @@
         <v>325</v>
       </c>
       <c r="U536" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V536" t="n">
         <v>45.81975</v>
@@ -37794,7 +37794,7 @@
         <v>325</v>
       </c>
       <c r="U537" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V537" t="n">
         <v>45.78418</v>
@@ -37864,7 +37864,7 @@
         <v>325</v>
       </c>
       <c r="U538" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V538" t="n">
         <v>45.63058</v>
@@ -37934,7 +37934,7 @@
         <v>325</v>
       </c>
       <c r="U539" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V539" t="n">
         <v>45.72058</v>
@@ -38004,7 +38004,7 @@
         <v>325</v>
       </c>
       <c r="U540" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V540" t="n">
         <v>45.74309</v>
@@ -38074,7 +38074,7 @@
         <v>325</v>
       </c>
       <c r="U541" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V541" t="n">
         <v>45.59558</v>
@@ -38144,7 +38144,7 @@
         <v>325</v>
       </c>
       <c r="U542" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V542" t="n">
         <v>45.67057</v>
@@ -38214,7 +38214,7 @@
         <v>325</v>
       </c>
       <c r="U543" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V543" t="n">
         <v>45.70003</v>
@@ -38284,7 +38284,7 @@
         <v>325</v>
       </c>
       <c r="U544" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V544" t="n">
         <v>45.67225</v>
@@ -38354,7 +38354,7 @@
         <v>325</v>
       </c>
       <c r="U545" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V545" t="n">
         <v>45.74448</v>
@@ -38424,7 +38424,7 @@
         <v>325</v>
       </c>
       <c r="U546" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V546" t="n">
         <v>45.60753</v>
@@ -38494,7 +38494,7 @@
         <v>325</v>
       </c>
       <c r="U547" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V547" t="n">
         <v>45.88225</v>
@@ -38564,7 +38564,7 @@
         <v>325</v>
       </c>
       <c r="U548" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V548" t="n">
         <v>45.94808</v>
@@ -38634,7 +38634,7 @@
         <v>325</v>
       </c>
       <c r="U549" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V549" t="n">
         <v>45.81447</v>
@@ -38704,7 +38704,7 @@
         <v>325</v>
       </c>
       <c r="U550" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V550" t="n">
         <v>45.98335</v>
@@ -38770,7 +38770,7 @@
         <v>325</v>
       </c>
       <c r="U551" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V551" t="n">
         <v>45.74642</v>
@@ -38840,7 +38840,7 @@
         <v>325</v>
       </c>
       <c r="U552" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V552" t="n">
         <v>45.40808</v>
@@ -38910,7 +38910,7 @@
         <v>325</v>
       </c>
       <c r="U553" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V553" t="n">
         <v>45.56587</v>
@@ -38980,7 +38980,7 @@
         <v>325</v>
       </c>
       <c r="U554" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V554" t="n">
         <v>45.52725</v>
@@ -39050,7 +39050,7 @@
         <v>325</v>
       </c>
       <c r="U555" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V555" t="n">
         <v>45.52197</v>
@@ -39120,7 +39120,7 @@
         <v>325</v>
       </c>
       <c r="U556" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V556" t="n">
         <v>45.54003</v>
@@ -39190,7 +39190,7 @@
         <v>325</v>
       </c>
       <c r="U557" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V557" t="n">
         <v>45.64723</v>
@@ -39260,7 +39260,7 @@
         <v>325</v>
       </c>
       <c r="U558" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V558" t="n">
         <v>45.68531</v>
@@ -39326,7 +39326,7 @@
         <v>325</v>
       </c>
       <c r="U559" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V559" t="n">
         <v>46.64809</v>
@@ -39396,7 +39396,7 @@
         <v>325</v>
       </c>
       <c r="U560" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V560" t="n">
         <v>46.58114</v>
@@ -39462,7 +39462,7 @@
         <v>325</v>
       </c>
       <c r="U561" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V561" t="n">
         <v>46.58393</v>
@@ -39528,7 +39528,7 @@
         <v>325</v>
       </c>
       <c r="U562" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V562" t="n">
         <v>46.78948</v>
@@ -39594,7 +39594,7 @@
         <v>325</v>
       </c>
       <c r="U563" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V563" t="n">
         <v>46.93753</v>
@@ -39660,7 +39660,7 @@
         <v>325</v>
       </c>
       <c r="U564" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V564" t="n">
         <v>46.84115</v>
@@ -39726,7 +39726,7 @@
         <v>325</v>
       </c>
       <c r="U565" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V565" t="n">
         <v>46.91447</v>
@@ -39792,7 +39792,7 @@
         <v>325</v>
       </c>
       <c r="U566" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V566" t="n">
         <v>46.85892</v>
@@ -39858,7 +39858,7 @@
         <v>325</v>
       </c>
       <c r="U567" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V567" t="n">
         <v>46.97837</v>
@@ -39928,7 +39928,7 @@
         <v>325</v>
       </c>
       <c r="U568" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V568" t="n">
         <v>46.98503</v>
@@ -39994,7 +39994,7 @@
         <v>325</v>
       </c>
       <c r="U569" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V569" t="n">
         <v>46.98392</v>
@@ -40064,7 +40064,7 @@
         <v>325</v>
       </c>
       <c r="U570" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V570" t="n">
         <v>46.9642</v>
@@ -40134,7 +40134,7 @@
         <v>325</v>
       </c>
       <c r="U571" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V571" t="n">
         <v>45.38336</v>
@@ -40204,7 +40204,7 @@
         <v>325</v>
       </c>
       <c r="U572" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V572" t="n">
         <v>45.40837</v>
@@ -40274,7 +40274,7 @@
         <v>325</v>
       </c>
       <c r="U573" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V573" t="n">
         <v>45.40558</v>
@@ -40344,7 +40344,7 @@
         <v>325</v>
       </c>
       <c r="U574" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V574" t="n">
         <v>45.23503</v>
@@ -40414,7 +40414,7 @@
         <v>325</v>
       </c>
       <c r="U575" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V575" t="n">
         <v>45.2003</v>
@@ -40484,7 +40484,7 @@
         <v>325</v>
       </c>
       <c r="U576" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V576" t="n">
         <v>45.40724</v>
@@ -40554,7 +40554,7 @@
         <v>325</v>
       </c>
       <c r="U577" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V577" t="n">
         <v>45.41669</v>
@@ -40624,7 +40624,7 @@
         <v>325</v>
       </c>
       <c r="U578" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V578" t="n">
         <v>45.74447</v>
@@ -40694,7 +40694,7 @@
         <v>325</v>
       </c>
       <c r="U579" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V579" t="n">
         <v>45.55502</v>
@@ -40764,7 +40764,7 @@
         <v>325</v>
       </c>
       <c r="U580" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V580" t="n">
         <v>45.51447</v>
@@ -40834,7 +40834,7 @@
         <v>325</v>
       </c>
       <c r="U581" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V581" t="n">
         <v>45.51114</v>
@@ -40904,7 +40904,7 @@
         <v>325</v>
       </c>
       <c r="U582" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V582" t="n">
         <v>45.57781</v>
@@ -40974,7 +40974,7 @@
         <v>325</v>
       </c>
       <c r="U583" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V583" t="n">
         <v>45.66059</v>
@@ -41044,7 +41044,7 @@
         <v>325</v>
       </c>
       <c r="U584" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V584" t="n">
         <v>45.61531</v>
@@ -41114,7 +41114,7 @@
         <v>325</v>
       </c>
       <c r="U585" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V585" t="n">
         <v>45.84947</v>
@@ -41184,7 +41184,7 @@
         <v>325</v>
       </c>
       <c r="U586" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V586" t="n">
         <v>45.73031</v>
@@ -41254,7 +41254,7 @@
         <v>325</v>
       </c>
       <c r="U587" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V587" t="n">
         <v>45.80197</v>
@@ -41324,7 +41324,7 @@
         <v>325</v>
       </c>
       <c r="U588" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V588" t="n">
         <v>45.78697</v>
@@ -41394,7 +41394,7 @@
         <v>325</v>
       </c>
       <c r="U589" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V589" t="n">
         <v>45.72836</v>
@@ -41464,7 +41464,7 @@
         <v>325</v>
       </c>
       <c r="U590" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V590" t="n">
         <v>45.56919</v>
@@ -41534,7 +41534,7 @@
         <v>325</v>
       </c>
       <c r="U591" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V591" t="n">
         <v>45.68114</v>
@@ -41604,7 +41604,7 @@
         <v>325</v>
       </c>
       <c r="U592" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V592" t="n">
         <v>46.62003</v>
@@ -41674,7 +41674,7 @@
         <v>325</v>
       </c>
       <c r="U593" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V593" t="n">
         <v>45.16725</v>
